--- a/docs/TEST_CHECKLIST_FULL.xlsx
+++ b/docs/TEST_CHECKLIST_FULL.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,77 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>트랙 #75: b7de919 / 3542e33 (시나리오 1~4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <f>== 트랙 #84 갱신 (2026-05-12) ===</f>
+        <v/>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>트랙 #84</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>SKIP 전수 진행 — 자격증명 의존 22건만 SKIP 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>진행 결과</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>PASS=15 / FAIL=0 / SKIP=26 / TOTAL=41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LLM 비용</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>~$0.05 (D-02/03/07/E-01/04 ~5회 호출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>운영 영향</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>0건 — mutation cycle 7건 모두 cleanup verified (B-03 Agent / F-02 Tool / B-04~07 PUT 원복 / 임시 ApiKey 회수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>운영 결함 발견</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Tools/Workflows axios 직접 사용 → JWT 미부착 (anti-patterns.md §11 위반) — 수정 완료</t>
         </is>
       </c>
     </row>

--- a/docs/TEST_CHECKLIST_FULL.xlsx
+++ b/docs/TEST_CHECKLIST_FULL.xlsx
@@ -5939,6 +5939,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -8156,6 +8157,8 @@
         <v/>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
@@ -8193,6 +8196,8 @@
         <v>477</v>
       </c>
     </row>
+    <row r="94"/>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
@@ -12596,22 +12601,22 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>DOM mounted=True | duration=1814ms | final=http://192.168.10.39:64005/analytics | net_issues=2: [{'url': 'http://192.168.10.39:64005/api/analytics/dashboard', 'status': 500}, {'url': 'http://192.168.10.39:64005/api/analytics/agents/21/stats?period=month', 'status': 500}] | console_errors=1: ['Error loading analytics data: y']</t>
+          <t>DOM mounted=True | duration=1808ms | final=http://192.168.10.39:64005/analytics | no console/network issues</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/dashboard / 운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/agents/21/stats?period=month</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:39</t>
+          <t>2026-05-12 17:01:15</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -12726,18 +12731,18 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/dashboard</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:39</t>
+          <t>2026-05-12 17:01:15</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -12785,18 +12790,18 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/dashboard</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:39</t>
+          <t>2026-05-12 17:01:15</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -12851,7 +12856,7 @@
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:39</t>
+          <t>2026-05-12 17:01:15</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -12906,7 +12911,7 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:39</t>
+          <t>2026-05-12 17:01:15</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -12958,18 +12963,18 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>[라이브 라우트 결과 인용] Analytics: FAIL</t>
+          <t>[트랙 #84-1] 직전 5xx fix 후 재검증 통과 — Analytics: PASS</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 (인용)</t>
+          <t>2026-05-12 (재검증)</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
@@ -24799,22 +24804,22 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>DOM mounted=True | duration=2079ms | final=http://192.168.10.39:64005/ | net_issues=2: [{'url': 'http://192.168.10.39:64005/api/analytics/dashboard', 'status': 500}, {'url': 'http://192.168.10.39:64005/api/analytics/usage-history?startDate=2026-05-05T06:32:26.335Z&amp;endDate=2026-05-12T06:32:26.33', 'status': 500}] | console_errors=2: ['Error loading dashboard stats: y']</t>
+          <t>DOM mounted=True | duration=2155ms | final=http://192.168.10.39:64005/ | no console/network issues</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/dashboard / 운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/usage-history?startDate=2026-05-05T06:3</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:25</t>
+          <t>2026-05-12 17:01:01</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -24925,18 +24930,18 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/dashboard</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:25</t>
+          <t>2026-05-12 17:01:01</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -24984,18 +24989,18 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/dashboard</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:25</t>
+          <t>2026-05-12 17:01:01</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -25050,7 +25055,7 @@
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:25</t>
+          <t>2026-05-12 17:01:01</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -25105,7 +25110,7 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:25</t>
+          <t>2026-05-12 17:01:01</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -25157,18 +25162,18 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>[라이브 라우트 결과 인용] Dashboard: FAIL</t>
+          <t>[트랙 #84-1] 직전 5xx fix 후 재검증 통과 — Dashboard: PASS</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 (인용)</t>
+          <t>2026-05-12 (재검증)</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
@@ -28581,22 +28586,22 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>DOM mounted=True | duration=1804ms | final=http://192.168.10.39:64005/pii-protection | net_issues=2: [{'url': 'http://192.168.10.39:64005/api/piidetectionlogs?page=1&amp;pageSize=20&amp;startDate=2026-04-12&amp;endDate=2026-05-12', 'status': 500}, {'url': 'http://192.168.10.39:64005/api/piidetectionlogs/statistics?startDate=2026-04-12&amp;endDate=2026-05-12', 'status': 500}] | console_errors=2: ['로그 로드 실패: y']</t>
+          <t>DOM mounted=True | duration=1787ms | final=http://192.168.10.39:64005/pii-protection | no console/network issues</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/piidetectionlogs?page=1&amp;pageSize=20&amp;startDate=202 / 운영 백엔드 결함: 500 http://192.168.10.39:64005/api/piidetectionlogs/statistics?startDate=2026-04-12&amp;</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:30</t>
+          <t>2026-05-12 17:02:05</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -28711,18 +28716,18 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/piidetectionlogs?page=1&amp;pageSize=20&amp;startDate=202</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:30</t>
+          <t>2026-05-12 17:02:05</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -28770,18 +28775,18 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/piidetectionlogs?page=1&amp;pageSize=20&amp;startDate=202</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:30</t>
+          <t>2026-05-12 17:02:05</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -28836,7 +28841,7 @@
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:30</t>
+          <t>2026-05-12 17:02:05</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -28891,7 +28896,7 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:30</t>
+          <t>2026-05-12 17:02:05</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -28943,18 +28948,18 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>[라이브 라우트 결과 인용] PiiProtection: FAIL</t>
+          <t>[트랙 #84-1] 직전 5xx fix 후 재검증 통과 — PiiProtection: PASS</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 (인용)</t>
+          <t>2026-05-12 (재검증)</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
@@ -36323,13 +36328,17 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>DOM mounted=True | duration=1778ms | final=http://192.168.10.39:64005/tools | net_issues=1: [{'url': 'http://192.168.10.39:64005/api/tools', 'status': 401}] | console_errors=1: ['Error loading tools: y']</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr"/>
+          <t>DOM mounted=True | duration=1794ms | final=http://192.168.10.39:64005/tools | no console/network issues</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+        </is>
+      </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:45</t>
+          <t>2026-05-12 17:02:20</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -36448,10 +36457,14 @@
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+        </is>
+      </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:45</t>
+          <t>2026-05-12 17:02:20</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -36503,10 +36516,14 @@
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+        </is>
+      </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:45</t>
+          <t>2026-05-12 17:02:20</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -36561,7 +36578,7 @@
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:45</t>
+          <t>2026-05-12 17:02:20</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -36616,7 +36633,7 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:45</t>
+          <t>2026-05-12 17:02:20</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -36834,22 +36851,22 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>DOM mounted=True | duration=1811ms | final=http://192.168.10.39:64005/usage-history | net_issues=1: [{'url': 'http://192.168.10.39:64005/api/analytics/usage-history?skip=0&amp;take=20&amp;startDate=2026-03-31T00:00:00.000Z&amp;endDate=2026-05', 'status': 500}] | console_errors=1: ['Error loading usages: y']</t>
+          <t>DOM mounted=True | duration=1800ms | final=http://192.168.10.39:64005/usage-history | no console/network issues</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/usage-history?skip=0&amp;take=20&amp;startDate=</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:24</t>
+          <t>2026-05-12 17:02:00</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -36964,18 +36981,18 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/usage-history?skip=0&amp;take=20&amp;startDate=</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:24</t>
+          <t>2026-05-12 17:02:00</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -37023,18 +37040,18 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>운영 백엔드 결함: 500 http://192.168.10.39:64005/api/analytics/usage-history?skip=0&amp;take=20&amp;startDate=</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:24</t>
+          <t>2026-05-12 17:02:00</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -37089,7 +37106,7 @@
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:24</t>
+          <t>2026-05-12 17:02:00</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -37144,7 +37161,7 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:24</t>
+          <t>2026-05-12 17:02:00</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -37196,18 +37213,18 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>[라이브 라우트 결과 인용] UsageHistory: FAIL</t>
+          <t>[트랙 #84-1] 직전 5xx fix 후 재검증 통과 — UsageHistory: PASS</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 (인용)</t>
+          <t>2026-05-12 (재검증)</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
@@ -38911,13 +38928,17 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>DOM mounted=True | duration=1780ms | final=http://192.168.10.39:64005/workflows | net_issues=1: [{'url': 'http://192.168.10.39:64005/api/workflows', 'status': 401}] | console_errors=1: ['Error loading workflows: y']</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr"/>
+          <t>DOM mounted=True | duration=1781ms | final=http://192.168.10.39:64005/workflows | no console/network issues</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+        </is>
+      </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:48</t>
+          <t>2026-05-12 17:02:23</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -39036,10 +39057,14 @@
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+        </is>
+      </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:48</t>
+          <t>2026-05-12 17:02:23</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -39091,10 +39116,14 @@
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+        </is>
+      </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:48</t>
+          <t>2026-05-12 17:02:23</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -39149,7 +39178,7 @@
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:48</t>
+          <t>2026-05-12 17:02:23</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -39204,7 +39233,7 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:33:48</t>
+          <t>2026-05-12 17:02:23</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">

--- a/docs/TEST_CHECKLIST_FULL.xlsx
+++ b/docs/TEST_CHECKLIST_FULL.xlsx
@@ -8382,10 +8382,14 @@
           <t>DOM mounted=True | duration=1801ms | final=http://192.168.10.39:64005/agents/builder</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:36</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -8504,10 +8508,14 @@
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:36</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -8559,10 +8567,14 @@
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:36</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -8898,10 +8910,14 @@
           <t>DOM mounted=True | duration=2727ms | final=http://192.168.10.39:64005/agents/chat</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:31</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -9020,10 +9036,14 @@
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:31</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -9075,10 +9095,14 @@
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:31</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -10328,10 +10352,14 @@
           <t>DOM mounted=True | duration=1813ms | final=http://192.168.10.39:64005/agents/multi-chat</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:34</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -10450,10 +10478,14 @@
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:34</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -10505,10 +10537,14 @@
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:34</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -12097,10 +12133,14 @@
           <t>DOM mounted=True | duration=1814ms | final=http://192.168.10.39:64005/agents</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:29</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -12215,10 +12255,14 @@
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:29</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -12270,10 +12314,14 @@
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>[트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
+        </is>
+      </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:32:29</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -36333,12 +36381,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건 | [트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 17:02:20</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -36459,12 +36507,12 @@
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건 | [트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 17:02:20</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -36518,12 +36566,12 @@
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건 | [트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 17:02:20</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
@@ -38933,12 +38981,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건 | [트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 17:02:23</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -39059,12 +39107,12 @@
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건 | [트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 17:02:23</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -39118,12 +39166,12 @@
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건</t>
+          <t>[트랙 #84-1] 직전 5xx/401 결함 fix 후 재검증 통과 — console/network 결함 0건 | [트랙 #84-2] 운영 mutation cleanup (Tools 8 + Agents 4 + ApiKey 1 DELETE, ApiKey3 docutil-runtime-key 보존) + ToolExecution 도메인 예외 분리 + AgentsController.CreateAgent ServiceId FK 사전 검증 + Dockerfile python3 추가 — 재배포 후 87 routes PASS 65 / FAIL 0 / SKIP 22, console errors 0, network 5xx 0</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12 17:02:23</t>
+          <t>2026-05-12 (트랙 #84-2 재검증)</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
